--- a/answer/results/result4.xlsx
+++ b/answer/results/result4.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0e75e46e7b854c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27c4fb3ae1d74faa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -322,7 +322,7 @@
         <x:v>A003</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>[27,37)</x:v>
+        <x:v>[28,38)</x:v>
       </x:c>
       <x:c r="C4"/>
       <x:c r="D4"/>
@@ -377,7 +377,7 @@
         <x:v>A008</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>[12,22)</x:v>
+        <x:v>[9,19)</x:v>
       </x:c>
       <x:c r="C9"/>
       <x:c r="D9"/>
@@ -388,7 +388,7 @@
         <x:v>A009</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>[74,84)</x:v>
+        <x:v>[75,85)</x:v>
       </x:c>
       <x:c r="C10"/>
       <x:c r="D10"/>
@@ -396,32 +396,32 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>A011</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>[70,80)</x:v>
-      </x:c>
-      <x:c r="C11"/>
+        <x:v>A010</x:v>
+      </x:c>
+      <x:c r="B11"/>
+      <x:c r="C11" t="str">
+        <x:v>[267,272)</x:v>
+      </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>A012</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>[31,41)</x:v>
-      </x:c>
-      <x:c r="C12"/>
+        <x:v>A011</x:v>
+      </x:c>
+      <x:c r="B12"/>
+      <x:c r="C12" t="str">
+        <x:v>[275,280)</x:v>
+      </x:c>
       <x:c r="D12"/>
       <x:c r="E12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>A014</x:v>
+        <x:v>A012</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>[6,16)</x:v>
+        <x:v>[36,46)</x:v>
       </x:c>
       <x:c r="C13"/>
       <x:c r="D13"/>
@@ -429,120 +429,120 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>A015</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>[30,40)</x:v>
-      </x:c>
-      <x:c r="C14"/>
+        <x:v>A013</x:v>
+      </x:c>
+      <x:c r="B14"/>
+      <x:c r="C14" t="str">
+        <x:v>[191,196)</x:v>
+      </x:c>
       <x:c r="D14"/>
       <x:c r="E14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>A017</x:v>
-      </x:c>
-      <x:c r="B15"/>
-      <x:c r="C15" t="str">
-        <x:v>[434,439)</x:v>
-      </x:c>
+        <x:v>A014</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>[6,16)</x:v>
+      </x:c>
+      <x:c r="C15"/>
       <x:c r="D15"/>
       <x:c r="E15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>A018</x:v>
-      </x:c>
-      <x:c r="B16"/>
-      <x:c r="C16" t="str">
-        <x:v>[448,453)</x:v>
-      </x:c>
+        <x:v>A015</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>[30,40)</x:v>
+      </x:c>
+      <x:c r="C16"/>
       <x:c r="D16"/>
       <x:c r="E16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>A019</x:v>
-      </x:c>
-      <x:c r="B17" t="str">
-        <x:v>[80,90)</x:v>
-      </x:c>
-      <x:c r="C17"/>
+        <x:v>A016</x:v>
+      </x:c>
+      <x:c r="B17"/>
+      <x:c r="C17" t="str">
+        <x:v>[418,423)</x:v>
+      </x:c>
       <x:c r="D17"/>
       <x:c r="E17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>B001</x:v>
-      </x:c>
-      <x:c r="B18"/>
-      <x:c r="C18" t="str">
-        <x:v>[19,22)</x:v>
-      </x:c>
+        <x:v>A018</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>[49,59)</x:v>
+      </x:c>
+      <x:c r="C18"/>
       <x:c r="D18"/>
       <x:c r="E18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>B002</x:v>
+        <x:v>A020</x:v>
       </x:c>
       <x:c r="B19"/>
       <x:c r="C19" t="str">
-        <x:v>[22,25)</x:v>
+        <x:v>[371,376)</x:v>
       </x:c>
       <x:c r="D19"/>
       <x:c r="E19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>B003</x:v>
+        <x:v>B001</x:v>
       </x:c>
       <x:c r="B20"/>
       <x:c r="C20" t="str">
-        <x:v>[28,31)</x:v>
+        <x:v>[19,22)</x:v>
       </x:c>
       <x:c r="D20"/>
       <x:c r="E20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>B004</x:v>
+        <x:v>B002</x:v>
       </x:c>
       <x:c r="B21"/>
       <x:c r="C21" t="str">
-        <x:v>[49,52)</x:v>
+        <x:v>[26,29)</x:v>
       </x:c>
       <x:c r="D21"/>
       <x:c r="E21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>B006</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>[75,90)</x:v>
-      </x:c>
-      <x:c r="C22"/>
+        <x:v>B003</x:v>
+      </x:c>
+      <x:c r="B22"/>
+      <x:c r="C22" t="str">
+        <x:v>[27,30)</x:v>
+      </x:c>
       <x:c r="D22"/>
       <x:c r="E22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>B007</x:v>
+        <x:v>B004</x:v>
       </x:c>
       <x:c r="B23"/>
       <x:c r="C23" t="str">
-        <x:v>[58,61)</x:v>
+        <x:v>[41,44)</x:v>
       </x:c>
       <x:c r="D23"/>
       <x:c r="E23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>B008</x:v>
+        <x:v>B005</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>[44,59)</x:v>
+        <x:v>[1,16)</x:v>
       </x:c>
       <x:c r="C24"/>
       <x:c r="D24"/>
@@ -550,76 +550,76 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>B009</x:v>
-      </x:c>
-      <x:c r="B25"/>
-      <x:c r="C25" t="str">
-        <x:v>[81,84)</x:v>
-      </x:c>
+        <x:v>B006</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>[75,90)</x:v>
+      </x:c>
+      <x:c r="C25"/>
       <x:c r="D25"/>
       <x:c r="E25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>B010</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>[15,30)</x:v>
-      </x:c>
-      <x:c r="C26"/>
+        <x:v>B007</x:v>
+      </x:c>
+      <x:c r="B26"/>
+      <x:c r="C26" t="str">
+        <x:v>[57,60)</x:v>
+      </x:c>
       <x:c r="D26"/>
       <x:c r="E26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>B011</x:v>
-      </x:c>
-      <x:c r="B27"/>
-      <x:c r="C27" t="str">
-        <x:v>[156,159)</x:v>
-      </x:c>
+        <x:v>B008</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>[45,60)</x:v>
+      </x:c>
+      <x:c r="C27"/>
       <x:c r="D27"/>
       <x:c r="E27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>B012</x:v>
-      </x:c>
-      <x:c r="B28" t="str">
-        <x:v>[45,60)</x:v>
-      </x:c>
-      <x:c r="C28"/>
+        <x:v>B009</x:v>
+      </x:c>
+      <x:c r="B28"/>
+      <x:c r="C28" t="str">
+        <x:v>[81,84)</x:v>
+      </x:c>
       <x:c r="D28"/>
       <x:c r="E28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>B013</x:v>
-      </x:c>
-      <x:c r="B29"/>
-      <x:c r="C29" t="str">
-        <x:v>[177,180)</x:v>
-      </x:c>
+        <x:v>B010</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>[15,30)</x:v>
+      </x:c>
+      <x:c r="C29"/>
       <x:c r="D29"/>
       <x:c r="E29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>B014</x:v>
+        <x:v>B011</x:v>
       </x:c>
       <x:c r="B30"/>
       <x:c r="C30" t="str">
-        <x:v>[189,192)</x:v>
+        <x:v>[158,161)</x:v>
       </x:c>
       <x:c r="D30"/>
       <x:c r="E30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>B015</x:v>
+        <x:v>B012</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>[9,24)</x:v>
+        <x:v>[45,60)</x:v>
       </x:c>
       <x:c r="C31"/>
       <x:c r="D31"/>
@@ -627,109 +627,109 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>B016</x:v>
+        <x:v>B013</x:v>
       </x:c>
       <x:c r="B32"/>
       <x:c r="C32" t="str">
-        <x:v>[230,233)</x:v>
+        <x:v>[182,185)</x:v>
       </x:c>
       <x:c r="D32"/>
       <x:c r="E32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>B017</x:v>
-      </x:c>
-      <x:c r="B33" t="str">
-        <x:v>[70,85)</x:v>
-      </x:c>
-      <x:c r="C33"/>
+        <x:v>B014</x:v>
+      </x:c>
+      <x:c r="B33"/>
+      <x:c r="C33" t="str">
+        <x:v>[188,191)</x:v>
+      </x:c>
       <x:c r="D33"/>
       <x:c r="E33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>B018</x:v>
-      </x:c>
-      <x:c r="B34"/>
-      <x:c r="C34" t="str">
-        <x:v>[228,231)</x:v>
-      </x:c>
+        <x:v>B015</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>[25,40)</x:v>
+      </x:c>
+      <x:c r="C34"/>
       <x:c r="D34"/>
       <x:c r="E34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>B019</x:v>
+        <x:v>B016</x:v>
       </x:c>
       <x:c r="B35"/>
-      <x:c r="C35"/>
+      <x:c r="C35" t="str">
+        <x:v>[232,235)</x:v>
+      </x:c>
       <x:c r="D35"/>
-      <x:c r="E35" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="E35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>B020</x:v>
-      </x:c>
-      <x:c r="B36"/>
-      <x:c r="C36" t="str">
-        <x:v>[119,122)</x:v>
-      </x:c>
+        <x:v>B017</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>[52,67)</x:v>
+      </x:c>
+      <x:c r="C36"/>
       <x:c r="D36"/>
       <x:c r="E36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>B021</x:v>
+        <x:v>B018</x:v>
       </x:c>
       <x:c r="B37"/>
       <x:c r="C37" t="str">
-        <x:v>[299,302)</x:v>
+        <x:v>[228,231)</x:v>
       </x:c>
       <x:c r="D37"/>
       <x:c r="E37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>B022</x:v>
-      </x:c>
-      <x:c r="B38" t="str">
-        <x:v>[67,82)</x:v>
-      </x:c>
-      <x:c r="C38"/>
+        <x:v>B019</x:v>
+      </x:c>
+      <x:c r="B38"/>
+      <x:c r="C38" t="str">
+        <x:v>[219,222)</x:v>
+      </x:c>
       <x:c r="D38"/>
       <x:c r="E38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>B023</x:v>
-      </x:c>
-      <x:c r="B39" t="str">
-        <x:v>[46,61)</x:v>
-      </x:c>
-      <x:c r="C39"/>
+        <x:v>B020</x:v>
+      </x:c>
+      <x:c r="B39"/>
+      <x:c r="C39" t="str">
+        <x:v>[119,122)</x:v>
+      </x:c>
       <x:c r="D39"/>
       <x:c r="E39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
-        <x:v>B024</x:v>
+        <x:v>B021</x:v>
       </x:c>
       <x:c r="B40"/>
-      <x:c r="C40" t="str">
-        <x:v>[306,309)</x:v>
-      </x:c>
+      <x:c r="C40"/>
       <x:c r="D40"/>
-      <x:c r="E40"/>
+      <x:c r="E40" t="str">
+        <x:v>是</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
-        <x:v>B025</x:v>
+        <x:v>B022</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>[25,40)</x:v>
+        <x:v>[75,90)</x:v>
       </x:c>
       <x:c r="C41"/>
       <x:c r="D41"/>
@@ -737,109 +737,109 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
-        <x:v>B026</x:v>
+        <x:v>B023</x:v>
       </x:c>
       <x:c r="B42"/>
       <x:c r="C42" t="str">
-        <x:v>[370,373)</x:v>
+        <x:v>[308,311)</x:v>
       </x:c>
       <x:c r="D42"/>
       <x:c r="E42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
-        <x:v>B027</x:v>
+        <x:v>B024</x:v>
       </x:c>
       <x:c r="B43"/>
       <x:c r="C43" t="str">
-        <x:v>[347,350)</x:v>
+        <x:v>[308,311)</x:v>
       </x:c>
       <x:c r="D43"/>
       <x:c r="E43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
-        <x:v>B028</x:v>
-      </x:c>
-      <x:c r="B44"/>
-      <x:c r="C44" t="str">
-        <x:v>[367,370)</x:v>
-      </x:c>
+        <x:v>B025</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>[6,21)</x:v>
+      </x:c>
+      <x:c r="C44"/>
       <x:c r="D44"/>
       <x:c r="E44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
-        <x:v>B029</x:v>
-      </x:c>
-      <x:c r="B45" t="str">
-        <x:v>[25,40)</x:v>
-      </x:c>
-      <x:c r="C45"/>
+        <x:v>B026</x:v>
+      </x:c>
+      <x:c r="B45"/>
+      <x:c r="C45" t="str">
+        <x:v>[370,373)</x:v>
+      </x:c>
       <x:c r="D45"/>
       <x:c r="E45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>B030</x:v>
-      </x:c>
-      <x:c r="B46" t="str">
-        <x:v>[6,21)</x:v>
-      </x:c>
-      <x:c r="C46"/>
+        <x:v>B027</x:v>
+      </x:c>
+      <x:c r="B46"/>
+      <x:c r="C46" t="str">
+        <x:v>[337,340)</x:v>
+      </x:c>
       <x:c r="D46"/>
       <x:c r="E46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
-        <x:v>B031</x:v>
+        <x:v>B028</x:v>
       </x:c>
       <x:c r="B47"/>
       <x:c r="C47" t="str">
-        <x:v>[418,421)</x:v>
+        <x:v>[360,363)</x:v>
       </x:c>
       <x:c r="D47"/>
       <x:c r="E47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
-        <x:v>B032</x:v>
-      </x:c>
-      <x:c r="B48" t="str">
-        <x:v>[62,77)</x:v>
-      </x:c>
+        <x:v>B029</x:v>
+      </x:c>
+      <x:c r="B48"/>
       <x:c r="C48"/>
       <x:c r="D48"/>
-      <x:c r="E48"/>
+      <x:c r="E48" t="str">
+        <x:v>是</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
-        <x:v>B033</x:v>
-      </x:c>
-      <x:c r="B49" t="str">
-        <x:v>[60,75)</x:v>
-      </x:c>
-      <x:c r="C49"/>
+        <x:v>B030</x:v>
+      </x:c>
+      <x:c r="B49"/>
+      <x:c r="C49" t="str">
+        <x:v>[386,389)</x:v>
+      </x:c>
       <x:c r="D49"/>
       <x:c r="E49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
-        <x:v>B034</x:v>
+        <x:v>B031</x:v>
       </x:c>
       <x:c r="B50"/>
       <x:c r="C50" t="str">
-        <x:v>[446,449)</x:v>
+        <x:v>[410,413)</x:v>
       </x:c>
       <x:c r="D50"/>
       <x:c r="E50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
-        <x:v>B035</x:v>
+        <x:v>B032</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>[6,21)</x:v>
+        <x:v>[76,91)</x:v>
       </x:c>
       <x:c r="C51"/>
       <x:c r="D51"/>
@@ -847,205 +847,205 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
-        <x:v>B036</x:v>
+        <x:v>B033</x:v>
       </x:c>
       <x:c r="B52"/>
-      <x:c r="C52" t="str">
-        <x:v>[497,500)</x:v>
-      </x:c>
+      <x:c r="C52"/>
       <x:c r="D52"/>
-      <x:c r="E52"/>
+      <x:c r="E52" t="str">
+        <x:v>是</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
-        <x:v>B037</x:v>
-      </x:c>
-      <x:c r="B53"/>
-      <x:c r="C53" t="str">
-        <x:v>[461,464)</x:v>
-      </x:c>
+        <x:v>B034</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>[25,40)</x:v>
+      </x:c>
+      <x:c r="C53"/>
       <x:c r="D53"/>
       <x:c r="E53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
-        <x:v>B038</x:v>
-      </x:c>
-      <x:c r="B54"/>
-      <x:c r="C54" t="str">
-        <x:v>[486,489)</x:v>
-      </x:c>
+        <x:v>B035</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>[20,35)</x:v>
+      </x:c>
+      <x:c r="C54"/>
       <x:c r="D54"/>
       <x:c r="E54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
-        <x:v>B039</x:v>
-      </x:c>
-      <x:c r="B55" t="str">
-        <x:v>[27,42)</x:v>
-      </x:c>
-      <x:c r="C55"/>
+        <x:v>B036</x:v>
+      </x:c>
+      <x:c r="B55"/>
+      <x:c r="C55" t="str">
+        <x:v>[497,500)</x:v>
+      </x:c>
       <x:c r="D55"/>
       <x:c r="E55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
-        <x:v>C001</x:v>
-      </x:c>
-      <x:c r="B56"/>
+        <x:v>B037</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>[49,64)</x:v>
+      </x:c>
       <x:c r="C56"/>
-      <x:c r="D56" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="D56"/>
       <x:c r="E56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
-        <x:v>C002</x:v>
-      </x:c>
-      <x:c r="B57"/>
+        <x:v>B038</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>[43,58)</x:v>
+      </x:c>
       <x:c r="C57"/>
-      <x:c r="D57" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="D57"/>
       <x:c r="E57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
-        <x:v>C003</x:v>
+        <x:v>B039</x:v>
       </x:c>
       <x:c r="B58"/>
       <x:c r="C58" t="str">
-        <x:v>[31,33)</x:v>
+        <x:v>[480,483)</x:v>
       </x:c>
       <x:c r="D58"/>
       <x:c r="E58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
-        <x:v>C004</x:v>
+        <x:v>B040</x:v>
       </x:c>
       <x:c r="B59"/>
-      <x:c r="C59"/>
-      <x:c r="D59" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>[426,429)</x:v>
+      </x:c>
+      <x:c r="D59"/>
       <x:c r="E59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
-        <x:v>C005</x:v>
+        <x:v>C001</x:v>
       </x:c>
       <x:c r="B60"/>
       <x:c r="C60"/>
       <x:c r="D60" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
-        <x:v>C006</x:v>
+        <x:v>C002</x:v>
       </x:c>
       <x:c r="B61"/>
       <x:c r="C61"/>
       <x:c r="D61" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
-        <x:v>C007</x:v>
-      </x:c>
-      <x:c r="B62" t="str">
-        <x:v>[45,48)</x:v>
-      </x:c>
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="B62"/>
       <x:c r="C62"/>
-      <x:c r="D62"/>
+      <x:c r="D62" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>C008</x:v>
+        <x:v>C004</x:v>
       </x:c>
       <x:c r="B63"/>
       <x:c r="C63"/>
       <x:c r="D63" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>C009</x:v>
+        <x:v>C005</x:v>
       </x:c>
       <x:c r="B64"/>
       <x:c r="C64"/>
       <x:c r="D64" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>C010</x:v>
+        <x:v>C006</x:v>
       </x:c>
       <x:c r="B65"/>
       <x:c r="C65"/>
       <x:c r="D65" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
-        <x:v>C012</x:v>
-      </x:c>
-      <x:c r="B66"/>
+        <x:v>C007</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>[45,48)</x:v>
+      </x:c>
       <x:c r="C66"/>
-      <x:c r="D66" t="n">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="D66"/>
       <x:c r="E66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
-        <x:v>C013</x:v>
+        <x:v>C008</x:v>
       </x:c>
       <x:c r="B67"/>
       <x:c r="C67"/>
       <x:c r="D67" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="str">
-        <x:v>C014</x:v>
+        <x:v>C009</x:v>
       </x:c>
       <x:c r="B68"/>
       <x:c r="C68"/>
       <x:c r="D68" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="str">
-        <x:v>C015</x:v>
-      </x:c>
-      <x:c r="B69" t="str">
-        <x:v>[60,63)</x:v>
-      </x:c>
+        <x:v>C010</x:v>
+      </x:c>
+      <x:c r="B69"/>
       <x:c r="C69"/>
-      <x:c r="D69"/>
+      <x:c r="D69" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="str">
-        <x:v>C016</x:v>
+        <x:v>C012</x:v>
       </x:c>
       <x:c r="B70"/>
       <x:c r="C70"/>
@@ -1056,54 +1056,54 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="str">
-        <x:v>C017</x:v>
-      </x:c>
-      <x:c r="B71" t="str">
-        <x:v>[45,48)</x:v>
-      </x:c>
+        <x:v>C013</x:v>
+      </x:c>
+      <x:c r="B71"/>
       <x:c r="C71"/>
-      <x:c r="D71"/>
+      <x:c r="D71" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="E71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="str">
-        <x:v>C018</x:v>
+        <x:v>C014</x:v>
       </x:c>
       <x:c r="B72"/>
       <x:c r="C72"/>
       <x:c r="D72" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="str">
-        <x:v>C019</x:v>
-      </x:c>
-      <x:c r="B73"/>
+        <x:v>C015</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>[60,63)</x:v>
+      </x:c>
       <x:c r="C73"/>
-      <x:c r="D73" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="D73"/>
       <x:c r="E73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="str">
-        <x:v>C020</x:v>
+        <x:v>C016</x:v>
       </x:c>
       <x:c r="B74"/>
       <x:c r="C74"/>
       <x:c r="D74" t="n">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="str">
-        <x:v>C021</x:v>
+        <x:v>C017</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>[97,100)</x:v>
+        <x:v>[45,48)</x:v>
       </x:c>
       <x:c r="C75"/>
       <x:c r="D75"/>
@@ -1111,10 +1111,10 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="str">
-        <x:v>C022</x:v>
+        <x:v>C018</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>[96,99)</x:v>
+        <x:v>[16,19)</x:v>
       </x:c>
       <x:c r="C76"/>
       <x:c r="D76"/>
@@ -1122,43 +1122,43 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
-        <x:v>C023</x:v>
-      </x:c>
-      <x:c r="B77" t="str">
-        <x:v>[67,70)</x:v>
-      </x:c>
+        <x:v>C019</x:v>
+      </x:c>
+      <x:c r="B77"/>
       <x:c r="C77"/>
-      <x:c r="D77"/>
+      <x:c r="D77" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="E77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
-        <x:v>C024</x:v>
+        <x:v>C020</x:v>
       </x:c>
       <x:c r="B78"/>
-      <x:c r="C78" t="str">
-        <x:v>[155,157)</x:v>
-      </x:c>
-      <x:c r="D78"/>
+      <x:c r="C78"/>
+      <x:c r="D78" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
-        <x:v>C025</x:v>
-      </x:c>
-      <x:c r="B79"/>
+        <x:v>C021</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>[97,100)</x:v>
+      </x:c>
       <x:c r="C79"/>
-      <x:c r="D79" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D79"/>
       <x:c r="E79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="str">
-        <x:v>C026</x:v>
+        <x:v>C022</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>[38,41)</x:v>
+        <x:v>[96,99)</x:v>
       </x:c>
       <x:c r="C80"/>
       <x:c r="D80"/>
@@ -1166,120 +1166,120 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="str">
-        <x:v>C027</x:v>
-      </x:c>
-      <x:c r="B81"/>
+        <x:v>C023</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>[67,70)</x:v>
+      </x:c>
       <x:c r="C81"/>
-      <x:c r="D81" t="n">
-        <x:v>16</x:v>
-      </x:c>
+      <x:c r="D81"/>
       <x:c r="E81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="str">
-        <x:v>C028</x:v>
-      </x:c>
-      <x:c r="B82"/>
-      <x:c r="C82" t="str">
-        <x:v>[163,165)</x:v>
-      </x:c>
+        <x:v>C024</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>[63,66)</x:v>
+      </x:c>
+      <x:c r="C82"/>
       <x:c r="D82"/>
       <x:c r="E82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="str">
-        <x:v>C029</x:v>
+        <x:v>C025</x:v>
       </x:c>
       <x:c r="B83"/>
       <x:c r="C83"/>
       <x:c r="D83" t="n">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="str">
-        <x:v>C030</x:v>
-      </x:c>
-      <x:c r="B84"/>
+        <x:v>C026</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>[38,41)</x:v>
+      </x:c>
       <x:c r="C84"/>
-      <x:c r="D84" t="n">
-        <x:v>13</x:v>
-      </x:c>
+      <x:c r="D84"/>
       <x:c r="E84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="str">
-        <x:v>C031</x:v>
-      </x:c>
-      <x:c r="B85"/>
+        <x:v>C027</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>[25,28)</x:v>
+      </x:c>
       <x:c r="C85"/>
       <x:c r="D85"/>
-      <x:c r="E85" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="E85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
-        <x:v>C032</x:v>
-      </x:c>
-      <x:c r="B86"/>
+        <x:v>C028</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>[19,22)</x:v>
+      </x:c>
       <x:c r="C86"/>
-      <x:c r="D86" t="n">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="D86"/>
       <x:c r="E86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
-        <x:v>C033</x:v>
-      </x:c>
-      <x:c r="B87" t="str">
-        <x:v>[64,67)</x:v>
-      </x:c>
+        <x:v>C029</x:v>
+      </x:c>
+      <x:c r="B87"/>
       <x:c r="C87"/>
-      <x:c r="D87"/>
+      <x:c r="D87" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>C034</x:v>
-      </x:c>
-      <x:c r="B88" t="str">
-        <x:v>[64,67)</x:v>
-      </x:c>
+        <x:v>C030</x:v>
+      </x:c>
+      <x:c r="B88"/>
       <x:c r="C88"/>
-      <x:c r="D88"/>
+      <x:c r="D88" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="E88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str">
-        <x:v>C035</x:v>
+        <x:v>C031</x:v>
       </x:c>
       <x:c r="B89"/>
       <x:c r="C89"/>
       <x:c r="D89" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
-        <x:v>C036</x:v>
+        <x:v>C032</x:v>
       </x:c>
       <x:c r="B90"/>
       <x:c r="C90"/>
       <x:c r="D90" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
-        <x:v>C037</x:v>
+        <x:v>C033</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>[22,25)</x:v>
+        <x:v>[70,73)</x:v>
       </x:c>
       <x:c r="C91"/>
       <x:c r="D91"/>
@@ -1287,10 +1287,10 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>C038</x:v>
+        <x:v>C034</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>[27,30)</x:v>
+        <x:v>[70,73)</x:v>
       </x:c>
       <x:c r="C92"/>
       <x:c r="D92"/>
@@ -1298,32 +1298,32 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
-        <x:v>C039</x:v>
-      </x:c>
-      <x:c r="B93" t="str">
-        <x:v>[6,9)</x:v>
-      </x:c>
-      <x:c r="C93"/>
+        <x:v>C035</x:v>
+      </x:c>
+      <x:c r="B93"/>
+      <x:c r="C93" t="str">
+        <x:v>[274,276)</x:v>
+      </x:c>
       <x:c r="D93"/>
       <x:c r="E93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" t="str">
-        <x:v>C040</x:v>
-      </x:c>
-      <x:c r="B94" t="str">
-        <x:v>[3,6)</x:v>
-      </x:c>
+        <x:v>C036</x:v>
+      </x:c>
+      <x:c r="B94"/>
       <x:c r="C94"/>
-      <x:c r="D94"/>
+      <x:c r="D94" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="E94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="str">
-        <x:v>C041</x:v>
+        <x:v>C037</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>[97,100)</x:v>
+        <x:v>[22,25)</x:v>
       </x:c>
       <x:c r="C95"/>
       <x:c r="D95"/>
@@ -1331,21 +1331,21 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="str">
-        <x:v>C042</x:v>
+        <x:v>C038</x:v>
       </x:c>
       <x:c r="B96"/>
-      <x:c r="C96"/>
-      <x:c r="D96" t="n">
-        <x:v>12</x:v>
-      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>[282,284)</x:v>
+      </x:c>
+      <x:c r="D96"/>
       <x:c r="E96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="str">
-        <x:v>C043</x:v>
+        <x:v>C039</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>[67,70)</x:v>
+        <x:v>[6,9)</x:v>
       </x:c>
       <x:c r="C97"/>
       <x:c r="D97"/>
@@ -1353,10 +1353,10 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="str">
-        <x:v>C044</x:v>
+        <x:v>C040</x:v>
       </x:c>
       <x:c r="B98" t="str">
-        <x:v>[61,64)</x:v>
+        <x:v>[3,6)</x:v>
       </x:c>
       <x:c r="C98"/>
       <x:c r="D98"/>
@@ -1364,54 +1364,54 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" t="str">
-        <x:v>C045</x:v>
+        <x:v>C041</x:v>
       </x:c>
       <x:c r="B99"/>
-      <x:c r="C99"/>
-      <x:c r="D99" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>[306,308)</x:v>
+      </x:c>
+      <x:c r="D99"/>
       <x:c r="E99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="str">
-        <x:v>C046</x:v>
+        <x:v>C042</x:v>
       </x:c>
       <x:c r="B100"/>
       <x:c r="C100"/>
       <x:c r="D100" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="str">
-        <x:v>C047</x:v>
+        <x:v>C043</x:v>
       </x:c>
       <x:c r="B101"/>
-      <x:c r="C101"/>
+      <x:c r="C101" t="str">
+        <x:v>[250,252)</x:v>
+      </x:c>
       <x:c r="D101"/>
-      <x:c r="E101" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="E101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="str">
-        <x:v>C049</x:v>
-      </x:c>
-      <x:c r="B102" t="str">
-        <x:v>[22,25)</x:v>
-      </x:c>
+        <x:v>C044</x:v>
+      </x:c>
+      <x:c r="B102"/>
       <x:c r="C102"/>
-      <x:c r="D102"/>
+      <x:c r="D102" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="E102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" t="str">
-        <x:v>C050</x:v>
+        <x:v>C045</x:v>
       </x:c>
       <x:c r="B103" t="str">
-        <x:v>[3,6)</x:v>
+        <x:v>[55,58)</x:v>
       </x:c>
       <x:c r="C103"/>
       <x:c r="D103"/>
@@ -1419,109 +1419,109 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" t="str">
-        <x:v>C051</x:v>
+        <x:v>C046</x:v>
       </x:c>
       <x:c r="B104"/>
       <x:c r="C104"/>
       <x:c r="D104" t="n">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="str">
-        <x:v>C052</x:v>
+        <x:v>C047</x:v>
       </x:c>
       <x:c r="B105"/>
       <x:c r="C105"/>
       <x:c r="D105" t="n">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" t="str">
-        <x:v>C053</x:v>
+        <x:v>C048</x:v>
       </x:c>
       <x:c r="B106"/>
-      <x:c r="C106"/>
-      <x:c r="D106" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>[344,346)</x:v>
+      </x:c>
+      <x:c r="D106"/>
       <x:c r="E106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" t="str">
-        <x:v>C055</x:v>
-      </x:c>
-      <x:c r="B107" t="str">
-        <x:v>[60,63)</x:v>
-      </x:c>
+        <x:v>C049</x:v>
+      </x:c>
+      <x:c r="B107"/>
       <x:c r="C107"/>
-      <x:c r="D107"/>
+      <x:c r="D107" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" t="str">
-        <x:v>C056</x:v>
-      </x:c>
-      <x:c r="B108"/>
+        <x:v>C050</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>[3,6)</x:v>
+      </x:c>
       <x:c r="C108"/>
-      <x:c r="D108" t="n">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="D108"/>
       <x:c r="E108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" t="str">
-        <x:v>C057</x:v>
-      </x:c>
-      <x:c r="B109" t="str">
-        <x:v>[24,27)</x:v>
-      </x:c>
+        <x:v>C051</x:v>
+      </x:c>
+      <x:c r="B109"/>
       <x:c r="C109"/>
-      <x:c r="D109"/>
+      <x:c r="D109" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="E109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" t="str">
-        <x:v>C059</x:v>
+        <x:v>C052</x:v>
       </x:c>
       <x:c r="B110"/>
       <x:c r="C110"/>
       <x:c r="D110" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" t="str">
-        <x:v>C060</x:v>
-      </x:c>
-      <x:c r="B111"/>
+        <x:v>C053</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>[67,70)</x:v>
+      </x:c>
       <x:c r="C111"/>
-      <x:c r="D111" t="n">
-        <x:v>18</x:v>
-      </x:c>
+      <x:c r="D111"/>
       <x:c r="E111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" t="str">
-        <x:v>C061</x:v>
+        <x:v>C054</x:v>
       </x:c>
       <x:c r="B112"/>
       <x:c r="C112"/>
       <x:c r="D112" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="str">
-        <x:v>C062</x:v>
+        <x:v>C055</x:v>
       </x:c>
       <x:c r="B113" t="str">
-        <x:v>[77,80)</x:v>
+        <x:v>[60,63)</x:v>
       </x:c>
       <x:c r="C113"/>
       <x:c r="D113"/>
@@ -1529,76 +1529,76 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" t="str">
-        <x:v>C063</x:v>
-      </x:c>
-      <x:c r="B114" t="str">
-        <x:v>[80,83)</x:v>
-      </x:c>
+        <x:v>C056</x:v>
+      </x:c>
+      <x:c r="B114"/>
       <x:c r="C114"/>
-      <x:c r="D114"/>
+      <x:c r="D114" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" t="str">
-        <x:v>C064</x:v>
-      </x:c>
-      <x:c r="B115"/>
+        <x:v>C057</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>[22,25)</x:v>
+      </x:c>
       <x:c r="C115"/>
-      <x:c r="D115" t="n">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="D115"/>
       <x:c r="E115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" t="str">
-        <x:v>C065</x:v>
-      </x:c>
-      <x:c r="B116"/>
+        <x:v>C058</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>[22,25)</x:v>
+      </x:c>
       <x:c r="C116"/>
-      <x:c r="D116" t="n">
-        <x:v>12</x:v>
-      </x:c>
+      <x:c r="D116"/>
       <x:c r="E116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" t="str">
-        <x:v>C066</x:v>
-      </x:c>
-      <x:c r="B117"/>
+        <x:v>C059</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>[19,22)</x:v>
+      </x:c>
       <x:c r="C117"/>
-      <x:c r="D117" t="n">
-        <x:v>17</x:v>
-      </x:c>
+      <x:c r="D117"/>
       <x:c r="E117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" t="str">
-        <x:v>C067</x:v>
-      </x:c>
-      <x:c r="B118" t="str">
-        <x:v>[24,27)</x:v>
-      </x:c>
+        <x:v>C060</x:v>
+      </x:c>
+      <x:c r="B118"/>
       <x:c r="C118"/>
-      <x:c r="D118"/>
+      <x:c r="D118" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="E118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" t="str">
-        <x:v>C068</x:v>
+        <x:v>C061</x:v>
       </x:c>
       <x:c r="B119"/>
       <x:c r="C119"/>
       <x:c r="D119" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" t="str">
-        <x:v>C069</x:v>
+        <x:v>C062</x:v>
       </x:c>
       <x:c r="B120" t="str">
-        <x:v>[21,24)</x:v>
+        <x:v>[95,98)</x:v>
       </x:c>
       <x:c r="C120"/>
       <x:c r="D120"/>
@@ -1606,32 +1606,32 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" t="str">
-        <x:v>C070</x:v>
-      </x:c>
-      <x:c r="B121" t="str">
-        <x:v>[0,3)</x:v>
-      </x:c>
+        <x:v>C064</x:v>
+      </x:c>
+      <x:c r="B121"/>
       <x:c r="C121"/>
-      <x:c r="D121"/>
+      <x:c r="D121" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="E121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" t="str">
-        <x:v>C071</x:v>
-      </x:c>
-      <x:c r="B122"/>
+        <x:v>C065</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>[64,67)</x:v>
+      </x:c>
       <x:c r="C122"/>
-      <x:c r="D122" t="n">
-        <x:v>14</x:v>
-      </x:c>
+      <x:c r="D122"/>
       <x:c r="E122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" t="str">
-        <x:v>C072</x:v>
+        <x:v>C066</x:v>
       </x:c>
       <x:c r="B123" t="str">
-        <x:v>[95,98)</x:v>
+        <x:v>[46,49)</x:v>
       </x:c>
       <x:c r="C123"/>
       <x:c r="D123"/>
@@ -1639,73 +1639,73 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" t="str">
-        <x:v>C073</x:v>
-      </x:c>
-      <x:c r="B124"/>
+        <x:v>C067</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>[40,43)</x:v>
+      </x:c>
       <x:c r="C124"/>
-      <x:c r="D124" t="n">
-        <x:v>13</x:v>
-      </x:c>
+      <x:c r="D124"/>
       <x:c r="E124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" t="str">
-        <x:v>C074</x:v>
+        <x:v>C068</x:v>
       </x:c>
       <x:c r="B125"/>
       <x:c r="C125"/>
       <x:c r="D125" t="n">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" t="str">
-        <x:v>C075</x:v>
+        <x:v>C069</x:v>
       </x:c>
       <x:c r="B126"/>
       <x:c r="C126"/>
       <x:c r="D126" t="n">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" t="str">
-        <x:v>C076</x:v>
-      </x:c>
-      <x:c r="B127"/>
+        <x:v>C070</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>[0,3)</x:v>
+      </x:c>
       <x:c r="C127"/>
-      <x:c r="D127" t="n">
-        <x:v>18</x:v>
-      </x:c>
+      <x:c r="D127"/>
       <x:c r="E127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" t="str">
-        <x:v>C077</x:v>
+        <x:v>C071</x:v>
       </x:c>
       <x:c r="B128"/>
       <x:c r="C128"/>
-      <x:c r="D128"/>
-      <x:c r="E128" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="D128" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" t="str">
-        <x:v>C078</x:v>
-      </x:c>
-      <x:c r="B129" t="str">
-        <x:v>[22,25)</x:v>
-      </x:c>
+        <x:v>C072</x:v>
+      </x:c>
+      <x:c r="B129"/>
       <x:c r="C129"/>
-      <x:c r="D129"/>
+      <x:c r="D129" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="E129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" t="str">
-        <x:v>C079</x:v>
+        <x:v>C073</x:v>
       </x:c>
       <x:c r="B130"/>
       <x:c r="C130"/>
@@ -1716,113 +1716,168 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" t="str">
-        <x:v>C080</x:v>
+        <x:v>C074</x:v>
       </x:c>
       <x:c r="B131"/>
       <x:c r="C131" t="str">
-        <x:v>[370,372)</x:v>
+        <x:v>[400,402)</x:v>
       </x:c>
       <x:c r="D131"/>
       <x:c r="E131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" t="str">
-        <x:v>C081</x:v>
-      </x:c>
-      <x:c r="B132"/>
-      <x:c r="C132" t="str">
-        <x:v>[482,484)</x:v>
-      </x:c>
+        <x:v>C075</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>[67,70)</x:v>
+      </x:c>
+      <x:c r="C132"/>
       <x:c r="D132"/>
       <x:c r="E132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" t="str">
-        <x:v>C082</x:v>
+        <x:v>C076</x:v>
       </x:c>
       <x:c r="B133"/>
       <x:c r="C133"/>
       <x:c r="D133" t="n">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" t="str">
-        <x:v>C083</x:v>
+        <x:v>C077</x:v>
       </x:c>
       <x:c r="B134"/>
       <x:c r="C134"/>
       <x:c r="D134" t="n">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" t="str">
-        <x:v>C084</x:v>
+        <x:v>C078</x:v>
       </x:c>
       <x:c r="B135"/>
       <x:c r="C135"/>
       <x:c r="D135" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" t="str">
-        <x:v>C085</x:v>
+        <x:v>C079</x:v>
       </x:c>
       <x:c r="B136"/>
       <x:c r="C136"/>
       <x:c r="D136" t="n">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" t="str">
-        <x:v>C086</x:v>
+        <x:v>C080</x:v>
       </x:c>
       <x:c r="B137"/>
       <x:c r="C137" t="str">
-        <x:v>[402,404)</x:v>
+        <x:v>[370,372)</x:v>
       </x:c>
       <x:c r="D137"/>
       <x:c r="E137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" t="str">
-        <x:v>C087</x:v>
+        <x:v>C081</x:v>
       </x:c>
       <x:c r="B138"/>
-      <x:c r="C138"/>
-      <x:c r="D138" t="n">
-        <x:v>12</x:v>
-      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>[484,486)</x:v>
+      </x:c>
+      <x:c r="D138"/>
       <x:c r="E138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" t="str">
-        <x:v>C089</x:v>
-      </x:c>
-      <x:c r="B139" t="str">
-        <x:v>[24,27)</x:v>
-      </x:c>
+        <x:v>C082</x:v>
+      </x:c>
+      <x:c r="B139"/>
       <x:c r="C139"/>
-      <x:c r="D139"/>
+      <x:c r="D139" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="E139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" t="str">
-        <x:v>C090</x:v>
+        <x:v>C085</x:v>
       </x:c>
       <x:c r="B140"/>
       <x:c r="C140"/>
       <x:c r="D140" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E140"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>C086</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>[40,43)</x:v>
+      </x:c>
+      <x:c r="C141"/>
+      <x:c r="D141"/>
+      <x:c r="E141"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>C087</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>[40,43)</x:v>
+      </x:c>
+      <x:c r="C142"/>
+      <x:c r="D142"/>
+      <x:c r="E142"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>C088</x:v>
+      </x:c>
+      <x:c r="B143"/>
+      <x:c r="C143"/>
+      <x:c r="D143" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E140"/>
+      <x:c r="E143"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>C089</x:v>
+      </x:c>
+      <x:c r="B144"/>
+      <x:c r="C144"/>
+      <x:c r="D144" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E144"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>C090</x:v>
+      </x:c>
+      <x:c r="B145"/>
+      <x:c r="C145"/>
+      <x:c r="D145" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E145"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
